--- a/education_surveys/048_study_sport_and_music_habits_survey--education_surveys.xlsx
+++ b/education_surveys/048_study_sport_and_music_habits_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This is the introduction page.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>study_habits</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Study Habits</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How often do you study?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sport_habits</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Sport Habits</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Which types of sports do you engage in?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sport_frequency</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Sport Frequency</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How many minutes do you spend on sports per week?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sport_frequency_other</t>
+          <t>sport_days_per_week</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>if_other</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Sport Days Per Week</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>How many days do you spend on sports per week?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +660,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>music_habits</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Music Habits</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Which types of music do you enjoy?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>music_habits_other</t>
+          <t>music_minutes_per_week</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>if_music</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Music Minutes Per Week</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>How many minutes do you spend on music per week?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sport_minutes_per_week</t>
+          <t>music_days_per_week</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sport_minutes_per_week</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Music Days Per Week</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>How many days do you spend on music per week?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sport_minutes_per_week_other</t>
+          <t>music_interests</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>if_minutes</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Music Interests</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>What are your music interests?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,46 +758,54 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sport_days_per_week</t>
+          <t>music_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sport_days_per_week</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Music Frequency</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>How often do you listen to music?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sport_days_per_week_other</t>
+          <t>study_frequency_scale</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>if_days</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Study Frequency Scale</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>What is your study frequency scale?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sport_frequency_scale</t>
+          <t>study_frequency</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sport_frequency_scale</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Study Frequency</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>How often do you study?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>music_minutes_per_week</t>
+          <t>sport_interests</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>music_minutes_per_week</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Sport Interests</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>What are your sport interests?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,274 +866,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>music_minutes_per_week_other</t>
+          <t>sport_frequency_scale</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>if_minutes</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Sport Frequency Scale</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>What is your sport frequency scale?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>music_days_per_week</t>
+          <t>music_interests_scale</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>music_days_per_week</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Music Interests Scale</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>What is your music interests scale?</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>music_days_per_week_other</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>if_days</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>music_frequency_scale</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>music_frequency_scale</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>music_interests</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>music_interests</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>music_frequency</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>music_frequency</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>music_habits_scale</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>music_habits_scale</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>music_frequency_other</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>if_music_frequency</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>study_days_per_week</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>study_days_per_week</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>study_days_per_week_other</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>if_days</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>study_frequency_scale</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>study_frequency_scale</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>study_frequency</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>study_frequency</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +928,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,238 +956,629 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sport_habits_choices</t>
+          <t>study_habits_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sport_habits_choices</t>
+          <t>study_habits_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>music_habits_choices</t>
+          <t>study_habits_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>music_habits_choices</t>
+          <t>study_habits_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sport_frequency_scale_choices</t>
+          <t>sport_habits_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>gymnastics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Gymnastics</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sport_frequency_scale_choices</t>
+          <t>sport_habits_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Swimming</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>music_frequency_scale_choices</t>
+          <t>sport_habits_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Soccer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>music_frequency_scale_choices</t>
+          <t>sport_habits_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tennis</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>music_habits_scale_choices</t>
+          <t>sport_habits_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Basketball</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>music_habits_scale_choices</t>
+          <t>sport_habits_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Volleyball</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>study_frequency_scale_choices</t>
+          <t>sport_habits_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cycling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cycling</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>study_frequency_scale_choices</t>
+          <t>sport_habits_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>running</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Running</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>study_frequency_choices</t>
+          <t>sport_habits_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>music_habits_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>classical</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Classical</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>music_habits_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pop</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>music_habits_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>jazz</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jazz</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>music_habits_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>music_habits_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>hip-hop</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hip-Hop</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>music_habits_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>music_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>music_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>music_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>music_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>study_frequency_scale_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>study_frequency_scale_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>study_frequency_scale_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>study_frequency_scale_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>very_low</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>study_frequency_choices</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>study_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sport_frequency_scale_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sport_frequency_scale_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sport_frequency_scale_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sport_frequency_scale_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>very_low</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>music_interests_scale_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>music_interests_scale_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>music_interests_scale_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>music_interests_scale_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>very_low</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
